--- a/03-成熟度评估/03-局部评估/06-单工序评估模板.xlsx
+++ b/03-成熟度评估/03-局部评估/06-单工序评估模板.xlsx
@@ -92,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -119,11 +119,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -147,6 +156,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,7 +540,13 @@
           <t>06-单工序评估模板</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -538,6 +554,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -545,13 +562,15 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>本模板为通用的单工序精益成熟度评估模板，可适用于紧固件制造工艺链中的任何工序或生产线。使用时根据具体工序的特点，参照已有的专项评估表（冷镦、搓丝、热处理、表面处理、包装）或自行填写。</t>
-        </is>
-      </c>
-    </row>
+          <t>本模板为通用的单工序精益成熟度评估模板，可适用于制造工艺链中的任何工序或生产线。使用时根据具体工序的特点，参照已有的专项评估表（机加工、精加工、热处理、表面处理、包装）或自行填写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -559,6 +578,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -566,6 +586,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -573,6 +594,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -580,6 +602,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -587,6 +610,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
@@ -594,6 +618,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -601,6 +626,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -608,6 +634,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -615,6 +642,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
@@ -636,6 +664,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
@@ -643,6 +672,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
@@ -678,6 +708,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
@@ -685,6 +716,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
@@ -692,6 +724,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
@@ -699,6 +732,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -706,6 +740,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
@@ -713,6 +748,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
@@ -720,6 +756,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
@@ -727,6 +764,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
@@ -734,6 +772,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
@@ -741,6 +780,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
@@ -748,6 +788,7 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
@@ -755,6 +796,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -1651,24 +1693,24 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>冷镦</t>
+          <t>机加工</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>模具寿命管理、钢丝来料检验、冲压力监控</t>
+          <t>模具寿命管理、棒料来料检验、冲压力监控</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>搓丝</t>
+          <t>精加工</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>通止规检测、螺纹精度控制、搓丝板磨损监控</t>
+          <t>量规检测、螺纹精度控制、加工刀具磨损监控</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1753,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>分选</t>
+          <t>装配</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1858,7 +1900,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>冷镦</t>
+          <t>机加工</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -1885,7 +1927,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>搓丝</t>
+          <t>精加工</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
